--- a/data/trans_orig/IP29A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP29A_2023-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,08</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,25</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>8.081693932352904</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>8.362939999779801</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>8.245212356037632</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,94; 10,73</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6,29; 11,66</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,67; 10,38</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>5.940418521576247</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>6.287375687805836</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6.665821537523597</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.73338354184519</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>11.66451392510375</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.37546682965398</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>8,74</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,45; 10,52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6,52; 9,5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7,32; 9,46</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>8.73946711190572</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7.745554265658494</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>8.255272333126902</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,99</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,27</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>7.448287204224689</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>6.524329852298203</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>7.319420790528238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,82; 9,19</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,22; 12,59</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8,27; 10,34</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.52060515630416</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.502495534074225</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.455389556997925</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,97 +661,162 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9,03</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,56</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>7.990843590137259</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10.70030462930414</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.270195746945332</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7,82; 10,46</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6,93; 9,33</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7,64; 9,5</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.817966330255219</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>9.22209243693359</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>8.265381516070642</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.187890353474117</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.58615349826882</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.34421524033506</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>9.02854013706588</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.978383974658708</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8.564994849338898</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7.824585070869458</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6.931056092571446</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>7.638105852808298</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.46482843862102</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9.325487353936547</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.497876917043925</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>8,61</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8,77</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,68</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7,83; 9,48</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,97; 9,64</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8,16; 9,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>8.611731252568058</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>8.765682518218622</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>8.684056477964486</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>7.833070151589217</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>7.969775667232789</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>8.155318453215974</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.483729182055642</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.642100439127596</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.270677110871977</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -794,12 +824,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
